--- a/Documents/Result.xlsx
+++ b/Documents/Result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmcuo\Desktop\battery_estimation\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39803CBA-AC20-40C5-B364-0D5419332EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21599CBA-30FC-4277-B661-5EE9F20AC497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12990" yWindow="0" windowWidth="24315" windowHeight="18795" xr2:uid="{F49EA110-F9F5-49A3-B89A-C5726EF2A64D}"/>
   </bookViews>
@@ -747,13 +747,27 @@
       <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="12">
+        <v>77.44</v>
+      </c>
+      <c r="D15" s="12">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="E15" s="12">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="F15" s="12">
+        <v>83.87</v>
+      </c>
+      <c r="G15" s="12">
+        <v>48.97</v>
+      </c>
+      <c r="H15" s="12">
+        <v>52.23</v>
+      </c>
+      <c r="I15" s="13">
+        <v>47.03</v>
+      </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">

--- a/Documents/Result.xlsx
+++ b/Documents/Result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmcuo\Desktop\battery_estimation\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21599CBA-30FC-4277-B661-5EE9F20AC497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD43B7-5902-4B27-933C-51FC5D4D8B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12990" yWindow="0" windowWidth="24315" windowHeight="18795" xr2:uid="{F49EA110-F9F5-49A3-B89A-C5726EF2A64D}"/>
   </bookViews>
@@ -710,13 +710,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="6">
-        <v>81.77</v>
+        <v>82.06</v>
       </c>
       <c r="D13" s="6">
         <v>84.65</v>
       </c>
       <c r="E13" s="6">
-        <v>74.23</v>
+        <v>77.77</v>
       </c>
       <c r="F13" s="6">
         <v>86.67</v>
@@ -736,7 +736,9 @@
         <v>3</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="9">
+        <v>20</v>
+      </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -748,13 +750,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="12">
-        <v>77.44</v>
+        <v>78.45</v>
       </c>
       <c r="D15" s="12">
         <v>71.400000000000006</v>
       </c>
       <c r="E15" s="12">
-        <v>74.599999999999994</v>
+        <v>75.13</v>
       </c>
       <c r="F15" s="12">
         <v>83.87</v>
@@ -776,5 +778,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>